--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,49 +44,13 @@
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
-    <t xml:space="preserve">hawthorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">western bulldogs</t>
+    <t xml:space="preserve">melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">port adelaide</t>
   </si>
   <si>
     <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kennedy Community Centre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast suns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collingwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">People First Stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adelaide crows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geelong cats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unley Oval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">west coast eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane lions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mineral Resources Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">port adelaide</t>
   </si>
   <si>
     <t xml:space="preserve">Casey Fields</t>
@@ -461,7 +425,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="15.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="22.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
@@ -469,7 +433,7 @@
     <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="26.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="24.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="17.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -521,16 +485,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>6.3</v>
+        <v>-30.3</v>
       </c>
       <c r="G2" t="n">
-        <v>7.1</v>
+        <v>-10.2</v>
       </c>
       <c r="H2" t="n">
-        <v>9.6</v>
+        <v>-34.1</v>
       </c>
       <c r="I2" t="n">
-        <v>76.1</v>
+        <v>95.1</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -538,7 +502,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -553,16 +517,16 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>-11.1</v>
+        <v>7.2</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1</v>
+        <v>3.1</v>
       </c>
       <c r="H3" t="n">
-        <v>-11.7</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>78.7</v>
+        <v>77.2</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -570,7 +534,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -585,16 +549,16 @@
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.2</v>
+        <v>-30.3</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.9</v>
+        <v>-12.5</v>
       </c>
       <c r="H4" t="n">
-        <v>-9.2</v>
+        <v>-34.2</v>
       </c>
       <c r="I4" t="n">
-        <v>85.5</v>
+        <v>87.8</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -602,7 +566,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -617,16 +581,16 @@
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>20.1</v>
+        <v>-48.3</v>
       </c>
       <c r="G5" t="n">
-        <v>11.4</v>
+        <v>-19.7</v>
       </c>
       <c r="H5" t="n">
-        <v>16.9</v>
+        <v>-47.3</v>
       </c>
       <c r="I5" t="n">
-        <v>81.2</v>
+        <v>89.4</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
@@ -649,147 +613,19 @@
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>-30.3</v>
+        <v>-16.2</v>
       </c>
       <c r="G6" t="n">
-        <v>-10.2</v>
+        <v>-9.5</v>
       </c>
       <c r="H6" t="n">
-        <v>-34.1</v>
+        <v>-14.2</v>
       </c>
       <c r="I6" t="n">
-        <v>95.1</v>
+        <v>73.3</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>17</v>
-      </c>
-      <c r="I7" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="J7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-30.3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-34.2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-48.3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-19.7</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-47.3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>89.4</v>
-      </c>
-      <c r="J9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-16.2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="J10" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,36 +12,192 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROD Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM-only Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLAYER-only Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projected Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venue</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+  <si>
+    <t xml:space="preserve">rating_as_of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_datetime_utc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model_version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected_margin_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_only_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_home_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_away_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">binary_preferred_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">binary_preferred_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">significant_change_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_team_disagreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_lineup_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_lineup_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cold_start_players</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_decay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-12T03:05:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawthorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">western bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kennedy Community Centre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aflw_joint_club_persistent_player_margin_prod_1.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOINT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-12T04:35:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast suns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collingwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People First Stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-12T05:05:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adelaide crows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unley Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-12T06:35:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">west coast eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane lions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mineral Resources Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13T02:35:00.000+0000</t>
   </si>
   <si>
     <t xml:space="preserve">melbourne</t>
@@ -50,12 +206,12 @@
     <t xml:space="preserve">port adelaide</t>
   </si>
   <si>
-    <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
     <t xml:space="preserve">Casey Fields</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-13T03:05:00.000+0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">richmond</t>
   </si>
   <si>
@@ -65,6 +221,9 @@
     <t xml:space="preserve">Windy Hill</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-13T04:35:00.000+0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydney swans</t>
   </si>
   <si>
@@ -74,6 +233,9 @@
     <t xml:space="preserve">Henson Park</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-13T05:05:00.000+0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">north melbourne</t>
   </si>
   <si>
@@ -81,6 +243,9 @@
   </si>
   <si>
     <t xml:space="preserve">Arden Street Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13T07:05:00.000+0000</t>
   </si>
   <si>
     <t xml:space="preserve">fremantle</t>
@@ -424,16 +589,47 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="15.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="22.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="19.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="5.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="17.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="26.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="17.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="51.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="21.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="14.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="15.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="20.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="16.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="19.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="18.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="21.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="15.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="20.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="20.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="13.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="16.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="13.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="22.71" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="23.71" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="15.71" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="23.71" hidden="0" customWidth="1"/>
+    <col min="29" max="29" width="24.71" hidden="0" customWidth="1"/>
+    <col min="30" max="30" width="18.71" hidden="0" customWidth="1"/>
+    <col min="31" max="31" width="18.71" hidden="0" customWidth="1"/>
+    <col min="32" max="32" width="21.71" hidden="0" customWidth="1"/>
+    <col min="33" max="33" width="21.71" hidden="0" customWidth="1"/>
+    <col min="34" max="34" width="18.71" hidden="0" customWidth="1"/>
+    <col min="35" max="35" width="14.71" hidden="0" customWidth="1"/>
+    <col min="36" max="36" width="20.71" hidden="0" customWidth="1"/>
+    <col min="37" max="37" width="22.71" hidden="0" customWidth="1"/>
+    <col min="38" max="38" width="21.71" hidden="0" customWidth="1"/>
+    <col min="39" max="39" width="17.71" hidden="0" customWidth="1"/>
+    <col min="40" max="40" width="19.71" hidden="0" customWidth="1"/>
+    <col min="41" max="41" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,165 +663,1223 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
+        <v>46274</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46277</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
+        <v>41</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-30.3</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-34.1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>95.1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
+        <v>42</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-6.27392606282578</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.27392606282578</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-6.27392606282578</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6.27392606282578</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-6.27392606282578</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-7.05565708517614</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7.05565708517614</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-9.59298520238913</v>
+      </c>
+      <c r="R2" t="n">
+        <v>9.59298520238913</v>
+      </c>
+      <c r="S2" t="n">
+        <v>76.092390946731</v>
+      </c>
+      <c r="T2" t="n">
+        <v>34.9092324419526</v>
+      </c>
+      <c r="U2" t="n">
+        <v>41.1831585047784</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-8.07058833206134</v>
+      </c>
+      <c r="W2" t="n">
+        <v>8.07058833206134</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-7.05565708517614</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-2.53732811721299</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-15.7509335233087</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>9.47700746048287</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
+        <v>46274</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46277</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
+        <v>49</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I3" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
+        <v>50</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11.0847352494739</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-11.0847352494739</v>
+      </c>
+      <c r="L3" t="n">
+        <v>11.0847352494739</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-11.0847352494739</v>
+      </c>
+      <c r="N3" t="n">
+        <v>11.0847352494739</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-6.09162703464608</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6.09162703464608</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>11.6718497408455</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-11.6718497408455</v>
+      </c>
+      <c r="S3" t="n">
+        <v>78.7015856183072</v>
+      </c>
+      <c r="T3" t="n">
+        <v>44.8931604338905</v>
+      </c>
+      <c r="U3" t="n">
+        <v>33.8084251844167</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01376367555056</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-1.01376367555056</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-6.09162703464608</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>17.7634767754916</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>2.60148924717283</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>8.48324600230103</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
+        <v>46274</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46277</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
+        <v>53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-30.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-34.2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8.15174784438369</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-8.15174784438369</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8.15174784438369</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-8.15174784438369</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8.15174784438369</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5.91222830932137</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-5.91222830932137</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>9.21826033382668</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-9.21826033382668</v>
+      </c>
+      <c r="S4" t="n">
+        <v>85.4709593114651</v>
+      </c>
+      <c r="T4" t="n">
+        <v>46.8113535779244</v>
+      </c>
+      <c r="U4" t="n">
+        <v>38.6596057335407</v>
+      </c>
+      <c r="V4" t="n">
+        <v>7.2346411191235</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-7.2346411191235</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5.91222830932137</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.30603202450531</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.375115689311177</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>8.52686353369487</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
+        <v>46274</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46277</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
+        <v>57</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-48.3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-19.7</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-47.3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>89.4</v>
-      </c>
-      <c r="J5" t="s">
-        <v>22</v>
+        <v>58</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-20.144657001771</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20.144657001771</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-20.144657001771</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20.144657001771</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-20.144657001771</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-11.3985139778257</v>
+      </c>
+      <c r="P5" t="n">
+        <v>11.3985139778257</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-16.9006642028633</v>
+      </c>
+      <c r="R5" t="n">
+        <v>16.9006642028633</v>
+      </c>
+      <c r="S5" t="n">
+        <v>81.2386774404696</v>
+      </c>
+      <c r="T5" t="n">
+        <v>30.5470102193493</v>
+      </c>
+      <c r="U5" t="n">
+        <v>50.6916672211203</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-13.5993740678407</v>
+      </c>
+      <c r="W5" t="n">
+        <v>13.5993740678407</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-11.3985139778257</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-5.50215022503752</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-9.63363169396369</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-10.5110253078073</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>46278</v>
       </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
       <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
+        <v>61</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-16.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
+        <v>62</v>
+      </c>
+      <c r="F6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.2991532681061</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-30.2991532681061</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.2991532681061</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-30.2991532681061</v>
+      </c>
+      <c r="N6" t="n">
+        <v>30.2991532681061</v>
+      </c>
+      <c r="O6" t="n">
+        <v>10.2482850640804</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-10.2482850640804</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>34.1250255845521</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-34.1250255845521</v>
+      </c>
+      <c r="S6" t="n">
+        <v>95.0736420870632</v>
+      </c>
+      <c r="T6" t="n">
+        <v>62.6863976775846</v>
+      </c>
+      <c r="U6" t="n">
+        <v>32.3872444094786</v>
+      </c>
+      <c r="V6" t="n">
+        <v>19.7989812722691</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-19.7989812722691</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>10.2482850640804</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>23.8767405204718</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>4.20260753069723</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>26.0965457374088</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-7.23018625825254</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.23018625825254</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-7.23018625825254</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7.23018625825254</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-7.23018625825254</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-3.11956893694359</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.11956893694359</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-17.0232896239248</v>
+      </c>
+      <c r="R7" t="n">
+        <v>17.0232896239248</v>
+      </c>
+      <c r="S7" t="n">
+        <v>77.2153791357885</v>
+      </c>
+      <c r="T7" t="n">
+        <v>34.992596438768</v>
+      </c>
+      <c r="U7" t="n">
+        <v>42.2227826970205</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-8.68105721173607</v>
+      </c>
+      <c r="W7" t="n">
+        <v>8.68105721173607</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-3.11956893694359</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-13.9037206869812</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>5.55837282075397</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-12.7885590790065</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30.3427882771885</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-30.3427882771885</v>
+      </c>
+      <c r="L8" t="n">
+        <v>30.3427882771885</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-30.3427882771885</v>
+      </c>
+      <c r="N8" t="n">
+        <v>30.3427882771885</v>
+      </c>
+      <c r="O8" t="n">
+        <v>12.4504027387485</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-12.4504027387485</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>34.2226848380813</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-34.2226848380813</v>
+      </c>
+      <c r="S8" t="n">
+        <v>87.8194790592403</v>
+      </c>
+      <c r="T8" t="n">
+        <v>59.0811336682143</v>
+      </c>
+      <c r="U8" t="n">
+        <v>28.7383453910259</v>
+      </c>
+      <c r="V8" t="n">
+        <v>21.1593155784816</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-21.1593155784816</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>12.4504027387485</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>21.7722820993328</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>6.05233847271209</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>24.2904498044764</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" t="n">
+        <v>48.3333625318544</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-48.3333625318544</v>
+      </c>
+      <c r="L9" t="n">
+        <v>48.3333625318544</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-48.3333625318544</v>
+      </c>
+      <c r="N9" t="n">
+        <v>48.3333625318544</v>
+      </c>
+      <c r="O9" t="n">
+        <v>19.7039939904408</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-19.7039939904408</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>47.2917808688835</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-47.2917808688835</v>
+      </c>
+      <c r="S9" t="n">
+        <v>89.3581822904533</v>
+      </c>
+      <c r="T9" t="n">
+        <v>68.8457724111539</v>
+      </c>
+      <c r="U9" t="n">
+        <v>20.5124098792994</v>
+      </c>
+      <c r="V9" t="n">
+        <v>30.7391087418179</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-30.7391087418179</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>19.7039939904408</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>27.5877868784427</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>13.0111594662626</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>35.3222030655918</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16.239328388771</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-16.239328388771</v>
+      </c>
+      <c r="L10" t="n">
+        <v>16.239328388771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-16.239328388771</v>
+      </c>
+      <c r="N10" t="n">
+        <v>16.239328388771</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9.5100830685521</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-9.5100830685521</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>14.2484398780757</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-14.2484398780757</v>
+      </c>
+      <c r="S10" t="n">
+        <v>73.2553693527821</v>
+      </c>
+      <c r="T10" t="n">
+        <v>44.7473488707765</v>
+      </c>
+      <c r="U10" t="n">
+        <v>28.5080204820055</v>
+      </c>
+      <c r="V10" t="n">
+        <v>11.4054257923615</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-11.4054257923615</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>9.5100830685521</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.73835680952362</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>5.07332614773844</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>11.1660022410326</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.975</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,22 +44,13 @@
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
-    <t xml:space="preserve">hawthorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north melbourne</t>
+    <t xml:space="preserve">collingwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats</t>
   </si>
   <si>
     <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cazalys Stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collingwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geelong cats</t>
   </si>
   <si>
     <t xml:space="preserve">Victoria Park</t>
@@ -506,7 +497,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -521,16 +512,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>47.3</v>
+        <v>25.8</v>
       </c>
       <c r="G2" t="n">
-        <v>27.3</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>51.9</v>
+        <v>23.9</v>
       </c>
       <c r="I2" t="n">
-        <v>82.3</v>
+        <v>78.9</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -553,16 +544,16 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>25.8</v>
+        <v>-26</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>-6.1</v>
       </c>
       <c r="H3" t="n">
-        <v>23.9</v>
+        <v>-30</v>
       </c>
       <c r="I3" t="n">
-        <v>78.9</v>
+        <v>90.3</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -585,16 +576,16 @@
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>-26</v>
+        <v>8.4</v>
       </c>
       <c r="G4" t="n">
-        <v>-6.1</v>
+        <v>-4.7</v>
       </c>
       <c r="H4" t="n">
-        <v>-30</v>
+        <v>12.9</v>
       </c>
       <c r="I4" t="n">
-        <v>90.3</v>
+        <v>93</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -617,16 +608,16 @@
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>8.4</v>
+        <v>-0.9</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.7</v>
+        <v>3.8</v>
       </c>
       <c r="H5" t="n">
-        <v>12.9</v>
+        <v>-1.7</v>
       </c>
       <c r="I5" t="n">
-        <v>93</v>
+        <v>73.7</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
@@ -634,7 +625,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -649,16 +640,16 @@
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7</v>
+        <v>-6.5</v>
       </c>
       <c r="I6" t="n">
-        <v>73.7</v>
+        <v>85.1</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
@@ -681,16 +672,16 @@
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4</v>
+        <v>-9.2</v>
       </c>
       <c r="H7" t="n">
-        <v>-6.5</v>
+        <v>-1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>85.1</v>
+        <v>80.3</v>
       </c>
       <c r="J7" t="s">
         <v>28</v>
@@ -713,16 +704,16 @@
         <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-9.2</v>
+        <v>1.3</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>80.3</v>
+        <v>75.8</v>
       </c>
       <c r="J8" t="s">
         <v>31</v>
@@ -745,51 +736,19 @@
         <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>6.3</v>
+        <v>-7.9</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3</v>
+        <v>-9.7</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>-8.8</v>
       </c>
       <c r="I9" t="n">
-        <v>75.8</v>
+        <v>85.6</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-9.7</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-8.8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>85.6</v>
-      </c>
-      <c r="J10" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,49 +44,13 @@
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
-    <t xml:space="preserve">collingwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geelong cats</t>
+    <t xml:space="preserve">greater western sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">richmond</t>
   </si>
   <si>
     <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carlton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey Fields</t>
-  </si>
-  <si>
-    <t xml:space="preserve">port adelaide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney swans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alberton Oval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fremantle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">western bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cockburn ARC Oval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">greater western sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">richmond</t>
   </si>
   <si>
     <t xml:space="preserve">Corroboree Group Oval Manuka</t>
@@ -497,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -512,16 +476,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>25.8</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>23.9</v>
+        <v>-6.5</v>
       </c>
       <c r="I2" t="n">
-        <v>78.9</v>
+        <v>85.1</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -529,7 +493,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -544,16 +508,16 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>-26</v>
+        <v>1.7</v>
       </c>
       <c r="G3" t="n">
-        <v>-6.1</v>
+        <v>-9.2</v>
       </c>
       <c r="H3" t="n">
-        <v>-30</v>
+        <v>-1.5</v>
       </c>
       <c r="I3" t="n">
-        <v>90.3</v>
+        <v>80.3</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -561,7 +525,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -576,16 +540,16 @@
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>8.4</v>
+        <v>6.3</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.7</v>
+        <v>1.3</v>
       </c>
       <c r="H4" t="n">
-        <v>12.9</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>93</v>
+        <v>75.8</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -593,7 +557,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -608,147 +572,19 @@
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9</v>
+        <v>-7.9</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8</v>
+        <v>-9.7</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7</v>
+        <v>-8.8</v>
       </c>
       <c r="I5" t="n">
-        <v>73.7</v>
+        <v>85.6</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>85.1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-9.2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="J7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-9.7</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-8.8</v>
-      </c>
-      <c r="I9" t="n">
-        <v>85.6</v>
-      </c>
-      <c r="J9" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,36 +12,204 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROD Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM-only Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLAYER-only Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projected Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venue</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+  <si>
+    <t xml:space="preserve">rating_as_of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_datetime_utc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model_version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected_margin_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_only_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_home_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_away_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">binary_preferred_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">binary_preferred_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">significant_change_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_team_disagreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_lineup_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_lineup_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cold_start_players</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_decay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-18T07:45:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawthorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cazalys Stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aflw_joint_club_persistent_player_margin_prod_1.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOINT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-19T02:35:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collingwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victoria Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-19T03:05:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carlton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casey Fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-19T04:35:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">port adelaide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney swans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alberton Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-19T05:05:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">western bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cockburn ARC Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-20T02:35:00.000+0000</t>
   </si>
   <si>
     <t xml:space="preserve">greater western sydney</t>
@@ -50,12 +218,12 @@
     <t xml:space="preserve">richmond</t>
   </si>
   <si>
-    <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
     <t xml:space="preserve">Corroboree Group Oval Manuka</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-20T03:05:00.000+0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">essendon</t>
   </si>
   <si>
@@ -65,6 +233,9 @@
     <t xml:space="preserve">Windy Hill</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-20T05:05:00.000+0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">st kilda</t>
   </si>
   <si>
@@ -72,6 +243,9 @@
   </si>
   <si>
     <t xml:space="preserve">RSEA Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-20T07:05:00.000+0000</t>
   </si>
   <si>
     <t xml:space="preserve">brisbane lions</t>
@@ -415,16 +589,47 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="17.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="19.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="26.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="28.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="5.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="17.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="28.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="51.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="21.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="14.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="15.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="20.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="16.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="19.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="18.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="21.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="15.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="20.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="20.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="13.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="16.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="13.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="22.71" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="23.71" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="15.71" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="23.71" hidden="0" customWidth="1"/>
+    <col min="29" max="29" width="24.71" hidden="0" customWidth="1"/>
+    <col min="30" max="30" width="18.71" hidden="0" customWidth="1"/>
+    <col min="31" max="31" width="18.71" hidden="0" customWidth="1"/>
+    <col min="32" max="32" width="21.71" hidden="0" customWidth="1"/>
+    <col min="33" max="33" width="21.71" hidden="0" customWidth="1"/>
+    <col min="34" max="34" width="18.71" hidden="0" customWidth="1"/>
+    <col min="35" max="35" width="14.71" hidden="0" customWidth="1"/>
+    <col min="36" max="36" width="20.71" hidden="0" customWidth="1"/>
+    <col min="37" max="37" width="22.71" hidden="0" customWidth="1"/>
+    <col min="38" max="38" width="21.71" hidden="0" customWidth="1"/>
+    <col min="39" max="39" width="17.71" hidden="0" customWidth="1"/>
+    <col min="40" max="40" width="19.71" hidden="0" customWidth="1"/>
+    <col min="41" max="41" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,133 +663,1223 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
+        <v>46281</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46283</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
+        <v>41</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>85.1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
+        <v>42</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-47.3278778432074</v>
+      </c>
+      <c r="K2" t="n">
+        <v>47.3278778432074</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-47.3278778432074</v>
+      </c>
+      <c r="M2" t="n">
+        <v>47.3278778432074</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-47.3278778432074</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-27.2585534448089</v>
+      </c>
+      <c r="P2" t="n">
+        <v>27.2585534448089</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-51.9259853531325</v>
+      </c>
+      <c r="R2" t="n">
+        <v>51.9259853531325</v>
+      </c>
+      <c r="S2" t="n">
+        <v>82.280701795951</v>
+      </c>
+      <c r="T2" t="n">
+        <v>17.4764119763718</v>
+      </c>
+      <c r="U2" t="n">
+        <v>64.8042898195792</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-37.1255262081383</v>
+      </c>
+      <c r="W2" t="n">
+        <v>37.1255262081383</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-27.2585534448089</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-24.6674319083236</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-16.146802569348</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-31.1810752738595</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
+        <v>46281</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46284</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
+        <v>49</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-9.2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
+        <v>50</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-25.7538904155103</v>
+      </c>
+      <c r="K3" t="n">
+        <v>25.7538904155103</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-25.7538904155103</v>
+      </c>
+      <c r="M3" t="n">
+        <v>25.7538904155103</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-25.7538904155103</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-8.00696018382076</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8.00696018382076</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-23.9346019863777</v>
+      </c>
+      <c r="R3" t="n">
+        <v>23.9346019863777</v>
+      </c>
+      <c r="S3" t="n">
+        <v>78.9219689077821</v>
+      </c>
+      <c r="T3" t="n">
+        <v>26.5840392461359</v>
+      </c>
+      <c r="U3" t="n">
+        <v>52.3379296616462</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-14.3780169048435</v>
+      </c>
+      <c r="W3" t="n">
+        <v>14.3780169048435</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-8.00696018382076</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-15.9276418025569</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-12.0831906962139</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-13.6706997192964</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
+        <v>46281</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46284</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
+        <v>53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.0479436814282</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-26.0479436814282</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0479436814282</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-26.0479436814282</v>
+      </c>
+      <c r="N4" t="n">
+        <v>26.0479436814282</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6.0590394401751</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-6.0590394401751</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>29.9958087286713</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-29.9958087286713</v>
+      </c>
+      <c r="S4" t="n">
+        <v>90.2528091259859</v>
+      </c>
+      <c r="T4" t="n">
+        <v>58.150376403707</v>
+      </c>
+      <c r="U4" t="n">
+        <v>32.1024327222788</v>
+      </c>
+      <c r="V4" t="n">
+        <v>15.6337471555736</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-15.6337471555736</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6.0590394401751</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>23.9367692884962</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>6.68981043484237</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>19.3581332465858</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-8.3551615645661</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.3551615645661</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-8.3551615645661</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8.3551615645661</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-8.3551615645661</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.67797267399424</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-4.67797267399424</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-12.9241071507211</v>
+      </c>
+      <c r="R5" t="n">
+        <v>12.9241071507211</v>
+      </c>
+      <c r="S5" t="n">
+        <v>93.0264351939622</v>
+      </c>
+      <c r="T5" t="n">
+        <v>42.3356368146981</v>
+      </c>
+      <c r="U5" t="n">
+        <v>50.6907983792642</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-2.36285925589191</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.36285925589191</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.67797267399424</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-17.6020798247154</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>16.5210084445073</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-24.8761700090734</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.870128693126938</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.870128693126938</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.870128693126938</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.870128693126938</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.870128693126938</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-3.798506632519</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.798506632519</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.70074394486602</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1.70074394486602</v>
+      </c>
+      <c r="S6" t="n">
+        <v>73.7316426738878</v>
+      </c>
+      <c r="T6" t="n">
+        <v>37.3008856835074</v>
+      </c>
+      <c r="U6" t="n">
+        <v>36.4307569903804</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-1.59880640156499</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.59880640156499</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-3.798506632519</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.49925057738502</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-11.2645616551281</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>12.134690348255</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B7" s="1" t="n">
         <v>46285</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-9.7</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-8.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>85.6</v>
-      </c>
-      <c r="J5" t="s">
-        <v>22</v>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.509223415169892</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.509223415169892</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.509223415169892</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.509223415169892</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.509223415169892</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-2.3722082239812</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.3722082239812</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6.48016677710361</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-6.48016677710361</v>
+      </c>
+      <c r="S7" t="n">
+        <v>85.1326132464681</v>
+      </c>
+      <c r="T7" t="n">
+        <v>42.3116949156491</v>
+      </c>
+      <c r="U7" t="n">
+        <v>42.820918330819</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.16874177645273</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-1.16874177645273</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-2.3722082239812</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.8523750010848</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-15.1839622062624</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>14.6747387910925</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1.6991558337462</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.6991558337462</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1.6991558337462</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.6991558337462</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-1.6991558337462</v>
+      </c>
+      <c r="O8" t="n">
+        <v>9.17301312574273</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-9.17301312574273</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.4946939007223</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-1.4946939007223</v>
+      </c>
+      <c r="S8" t="n">
+        <v>80.2538198607699</v>
+      </c>
+      <c r="T8" t="n">
+        <v>39.2773320135118</v>
+      </c>
+      <c r="U8" t="n">
+        <v>40.976487847258</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.10168543573455</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-6.10168543573455</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9.17301312574273</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-7.67831922502043</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.786287507541632</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.912868326204564</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-6.29295887295439</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.29295887295439</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-6.29295887295439</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6.29295887295439</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-6.29295887295439</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-1.25286300869742</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25286300869742</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-6.00479235211446</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6.00479235211446</v>
+      </c>
+      <c r="S9" t="n">
+        <v>75.7573395302738</v>
+      </c>
+      <c r="T9" t="n">
+        <v>34.7321903286597</v>
+      </c>
+      <c r="U9" t="n">
+        <v>41.0251492016141</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-3.15363474606424</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.15363474606424</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1.25286300869742</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-4.75192934341704</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>4.26407783281614</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-10.5570367057705</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7.88224431112858</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-7.88224431112858</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.88224431112858</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-7.88224431112858</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.88224431112858</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9.68078172557175</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-9.68078172557175</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8.84161265761552</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-8.84161265761552</v>
+      </c>
+      <c r="S10" t="n">
+        <v>85.5924828697781</v>
+      </c>
+      <c r="T10" t="n">
+        <v>46.7373635904533</v>
+      </c>
+      <c r="U10" t="n">
+        <v>38.8551192793247</v>
+      </c>
+      <c r="V10" t="n">
+        <v>9.34511409838926</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-9.34511409838926</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>9.68078172557175</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.839169067956231</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>11.866962184488</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-3.98471787335941</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.975</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -42,18 +42,6 @@
   </si>
   <si>
     <t xml:space="preserve">Venue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geelong cats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hawthorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provisional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMHBA Stadium</t>
   </si>
   <si>
     <t xml:space="preserve">essendon</t>
@@ -506,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -521,16 +509,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>-19.9</v>
+        <v>-4</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.2</v>
+        <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>-23.5</v>
+        <v>-9.2</v>
       </c>
       <c r="I2" t="n">
-        <v>83</v>
+        <v>73.9</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -547,25 +535,25 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-17.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="J3" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-9.2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>73.9</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -573,31 +561,31 @@
         <v>46290</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-26.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-34.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>85.1</v>
+      </c>
+      <c r="J4" t="s">
         <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-17.7</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-19.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="J4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -605,63 +593,63 @@
         <v>46290</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>-26.3</v>
+        <v>7.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-13.4</v>
+        <v>13.3</v>
       </c>
       <c r="H5" t="n">
-        <v>-34.7</v>
+        <v>7.2</v>
       </c>
       <c r="I5" t="n">
-        <v>85.1</v>
+        <v>87.8</v>
       </c>
       <c r="J5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="J6" t="s">
         <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="J6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -669,31 +657,31 @@
         <v>46292</v>
       </c>
       <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J7" t="s">
         <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="J7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -701,31 +689,31 @@
         <v>46292</v>
       </c>
       <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>86.1</v>
+      </c>
+      <c r="J8" t="s">
         <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-11.1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-12</v>
-      </c>
-      <c r="I8" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -733,63 +721,31 @@
         <v>46292</v>
       </c>
       <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
         <v>32</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-15.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="J9" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>86.1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-15.1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="I10" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="J10" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,76 +44,52 @@
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
-    <t xml:space="preserve">essendon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">west coast eagles</t>
+    <t xml:space="preserve">collingwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">greater western sydney</t>
   </si>
   <si>
     <t xml:space="preserve">Previous</t>
   </si>
   <si>
-    <t xml:space="preserve">Windy Hill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">western bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">port adelaide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission Whitten Oval</t>
+    <t xml:space="preserve">Victoria Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adelaide crows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unley Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney swans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane lions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henson Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast suns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st kilda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People First Stadium</t>
   </si>
   <si>
     <t xml:space="preserve">carlton</t>
   </si>
   <si>
-    <t xml:space="preserve">richmond</t>
+    <t xml:space="preserve">hawthorn</t>
   </si>
   <si>
     <t xml:space="preserve">IKON Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collingwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">greater western sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adelaide crows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fremantle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unley Oval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney swans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane lions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henson Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast suns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st kilda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">People First Stadium</t>
   </si>
 </sst>
 </file>
@@ -449,7 +425,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="15.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="22.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
@@ -494,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -509,16 +485,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>-4</v>
+        <v>-6.9</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1</v>
+        <v>-6.2</v>
       </c>
       <c r="H2" t="n">
-        <v>-9.2</v>
+        <v>-7.9</v>
       </c>
       <c r="I2" t="n">
-        <v>73.9</v>
+        <v>81.5</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -526,7 +502,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -541,16 +517,16 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>-17.7</v>
+        <v>-11.1</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.9</v>
+        <v>-6.9</v>
       </c>
       <c r="H3" t="n">
-        <v>-19.5</v>
+        <v>-12</v>
       </c>
       <c r="I3" t="n">
-        <v>87.5</v>
+        <v>78.3</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -558,7 +534,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -573,16 +549,16 @@
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>-26.3</v>
+        <v>10.3</v>
       </c>
       <c r="G4" t="n">
-        <v>-13.4</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>-34.7</v>
+        <v>10.3</v>
       </c>
       <c r="I4" t="n">
-        <v>85.1</v>
+        <v>86.1</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -590,7 +566,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -605,30 +581,30 @@
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>7.5</v>
+        <v>-15.1</v>
       </c>
       <c r="G5" t="n">
-        <v>13.3</v>
+        <v>8.4</v>
       </c>
       <c r="H5" t="n">
-        <v>7.2</v>
+        <v>-11.9</v>
       </c>
       <c r="I5" t="n">
-        <v>87.8</v>
+        <v>81.8</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -637,115 +613,19 @@
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.9</v>
+        <v>-13.2</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.2</v>
+        <v>-7.4</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.9</v>
+        <v>-17.8</v>
       </c>
       <c r="I6" t="n">
-        <v>81.5</v>
+        <v>84.5</v>
       </c>
       <c r="J6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B7" t="s">
         <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-11.1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-12</v>
-      </c>
-      <c r="I7" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9</v>
-      </c>
-      <c r="H8" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>86.1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-15.1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="J9" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,49 +44,13 @@
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
-    <t xml:space="preserve">collingwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">greater western sydney</t>
+    <t xml:space="preserve">carlton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawthorn</t>
   </si>
   <si>
     <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adelaide crows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fremantle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unley Oval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney swans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane lions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henson Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast suns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st kilda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">People First Stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carlton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hawthorn</t>
   </si>
   <si>
     <t xml:space="preserve">IKON Park</t>
@@ -425,15 +389,15 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="15.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="22.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="9.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="19.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="26.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="20.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="9.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +434,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -485,147 +449,19 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.9</v>
+        <v>-13.2</v>
       </c>
       <c r="G2" t="n">
-        <v>-6.2</v>
+        <v>-7.4</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.9</v>
+        <v>-17.8</v>
       </c>
       <c r="I2" t="n">
-        <v>81.5</v>
+        <v>84.5</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-11.1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-12</v>
-      </c>
-      <c r="I3" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>86.1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-15.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="I5" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="J5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-13.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-17.8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,16 +44,79 @@
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
-    <t xml:space="preserve">carlton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hawthorn</t>
+    <t xml:space="preserve">richmond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats</t>
   </si>
   <si>
     <t xml:space="preserve">Previous</t>
   </si>
   <si>
     <t xml:space="preserve">IKON Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">greater western sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">essendon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henson Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">western bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st kilda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mars Stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane lions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast suns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brighton Homes Arena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">port adelaide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adelaide crows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alberton Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney swans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arden Street Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collingwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victoria Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">west coast eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sullivan Logistics Stadium</t>
   </si>
 </sst>
 </file>
@@ -389,15 +452,15 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="9.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="19.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="26.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="9.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="26.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,7 +497,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -449,19 +512,243 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>-13.2</v>
+        <v>31.2</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.4</v>
+        <v>8.5</v>
       </c>
       <c r="H2" t="n">
-        <v>-17.8</v>
+        <v>38.2</v>
       </c>
       <c r="I2" t="n">
-        <v>84.5</v>
+        <v>83.9</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-29.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-29.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-26.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>87.4</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-44</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-26.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-51.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="J7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>79.9</v>
+      </c>
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,22 +44,13 @@
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
-    <t xml:space="preserve">richmond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geelong cats</t>
+    <t xml:space="preserve">greater western sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">essendon</t>
   </si>
   <si>
     <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IKON Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">greater western sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">essendon</t>
   </si>
   <si>
     <t xml:space="preserve">Henson Park</t>
@@ -497,7 +488,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -512,16 +503,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>31.2</v>
+        <v>11.3</v>
       </c>
       <c r="G2" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="H2" t="n">
-        <v>38.2</v>
+        <v>17.3</v>
       </c>
       <c r="I2" t="n">
-        <v>83.9</v>
+        <v>82.5</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -544,16 +535,16 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>11.3</v>
+        <v>-29.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5</v>
+        <v>-10.2</v>
       </c>
       <c r="H3" t="n">
-        <v>17.3</v>
+        <v>-29.7</v>
       </c>
       <c r="I3" t="n">
-        <v>82.5</v>
+        <v>75.5</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -576,16 +567,16 @@
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>-29.5</v>
+        <v>-13.9</v>
       </c>
       <c r="G4" t="n">
-        <v>-10.2</v>
+        <v>-26.6</v>
       </c>
       <c r="H4" t="n">
-        <v>-29.7</v>
+        <v>-16.4</v>
       </c>
       <c r="I4" t="n">
-        <v>75.5</v>
+        <v>87.4</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -608,16 +599,16 @@
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>-13.9</v>
+        <v>16.1</v>
       </c>
       <c r="G5" t="n">
-        <v>-26.6</v>
+        <v>0.9</v>
       </c>
       <c r="H5" t="n">
-        <v>-16.4</v>
+        <v>19.1</v>
       </c>
       <c r="I5" t="n">
-        <v>87.4</v>
+        <v>92.3</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
@@ -625,7 +616,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -640,16 +631,16 @@
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>16.1</v>
+        <v>-44</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9</v>
+        <v>-26.5</v>
       </c>
       <c r="H6" t="n">
-        <v>19.1</v>
+        <v>-51.4</v>
       </c>
       <c r="I6" t="n">
-        <v>92.3</v>
+        <v>85.5</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
@@ -672,16 +663,16 @@
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>-44</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>-26.5</v>
+        <v>19.7</v>
       </c>
       <c r="H7" t="n">
-        <v>-51.4</v>
+        <v>31.6</v>
       </c>
       <c r="I7" t="n">
-        <v>85.5</v>
+        <v>79.9</v>
       </c>
       <c r="J7" t="s">
         <v>28</v>
@@ -704,51 +695,19 @@
         <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>11.3</v>
       </c>
       <c r="G8" t="n">
-        <v>19.7</v>
+        <v>0.8</v>
       </c>
       <c r="H8" t="n">
-        <v>31.6</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>79.9</v>
+        <v>74.2</v>
       </c>
       <c r="J8" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="J9" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -44,49 +44,13 @@
     <t xml:space="preserve">Venue</t>
   </si>
   <si>
-    <t xml:space="preserve">greater western sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">essendon</t>
+    <t xml:space="preserve">north melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney swans</t>
   </si>
   <si>
     <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henson Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">western bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st kilda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mars Stadium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane lions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast suns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brighton Homes Arena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">port adelaide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adelaide crows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alberton Oval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney swans</t>
   </si>
   <si>
     <t xml:space="preserve">Arden Street Oval</t>
@@ -443,8 +407,8 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="19.71" hidden="0" customWidth="1"/>
@@ -488,7 +452,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -503,16 +467,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>11.3</v>
+        <v>-44</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5</v>
+        <v>-26.5</v>
       </c>
       <c r="H2" t="n">
-        <v>17.3</v>
+        <v>-51.4</v>
       </c>
       <c r="I2" t="n">
-        <v>82.5</v>
+        <v>85.5</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -520,7 +484,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -535,16 +499,16 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>-29.5</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>-10.2</v>
+        <v>19.7</v>
       </c>
       <c r="H3" t="n">
-        <v>-29.7</v>
+        <v>31.6</v>
       </c>
       <c r="I3" t="n">
-        <v>75.5</v>
+        <v>79.9</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -552,7 +516,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -567,147 +531,19 @@
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>-13.9</v>
+        <v>11.3</v>
       </c>
       <c r="G4" t="n">
-        <v>-26.6</v>
+        <v>0.8</v>
       </c>
       <c r="H4" t="n">
-        <v>-16.4</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>87.4</v>
+        <v>74.2</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H5" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="J5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-44</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-26.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-51.4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>31</v>
-      </c>
-      <c r="G7" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>79.9</v>
-      </c>
-      <c r="J7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I8" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFLW_upcoming_projections.xlsx
+++ b/files/AFLW_upcoming_projections.xlsx
@@ -12,36 +12,216 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Team List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROD Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM-only Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLAYER-only Projected Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projected Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venue</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+  <si>
+    <t xml:space="preserve">rating_as_of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_datetime_utc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model_version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected_margin_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prod_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">previous_prod_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_only_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_only_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_home_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projected_away_score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_home_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hybrid_weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">binary_preferred_model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">binary_preferred_margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">significant_change_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_team_disagreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_lineup_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_lineup_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">away_team_list_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cold_start_players</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_lineup_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_team_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_player_lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_decay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01T09:15:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carlton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawthorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IKON Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aflw_joint_club_persistent_player_margin_prod_1.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOINT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provisional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-02T09:15:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">richmond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-03T03:05:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">greater western sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">essendon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henson Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-03T05:05:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">western bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st kilda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mars Stadium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-03T07:05:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane lions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast suns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brighton Homes Arena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-03T09:15:00.000+0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">port adelaide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adelaide crows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alberton Oval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04T02:05:00.000+0000</t>
   </si>
   <si>
     <t xml:space="preserve">north melbourne</t>
@@ -50,12 +230,12 @@
     <t xml:space="preserve">sydney swans</t>
   </si>
   <si>
-    <t xml:space="preserve">Previous</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arden Street Oval</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-10-04T04:05:00.000+0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">collingwood</t>
   </si>
   <si>
@@ -63,6 +243,9 @@
   </si>
   <si>
     <t xml:space="preserve">Victoria Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04T06:05:00.000+0000</t>
   </si>
   <si>
     <t xml:space="preserve">west coast eagles</t>
@@ -406,16 +589,47 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="19.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="26.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="26.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="5.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="15.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="26.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="51.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="21.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="14.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="15.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="20.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="16.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="19.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="18.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="21.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="15.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="20.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="20.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="13.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="16.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="13.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="22.71" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="23.71" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="15.71" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="23.71" hidden="0" customWidth="1"/>
+    <col min="29" max="29" width="24.71" hidden="0" customWidth="1"/>
+    <col min="30" max="30" width="18.71" hidden="0" customWidth="1"/>
+    <col min="31" max="31" width="18.71" hidden="0" customWidth="1"/>
+    <col min="32" max="32" width="21.71" hidden="0" customWidth="1"/>
+    <col min="33" max="33" width="21.71" hidden="0" customWidth="1"/>
+    <col min="34" max="34" width="18.71" hidden="0" customWidth="1"/>
+    <col min="35" max="35" width="14.71" hidden="0" customWidth="1"/>
+    <col min="36" max="36" width="20.71" hidden="0" customWidth="1"/>
+    <col min="37" max="37" width="22.71" hidden="0" customWidth="1"/>
+    <col min="38" max="38" width="21.71" hidden="0" customWidth="1"/>
+    <col min="39" max="39" width="17.71" hidden="0" customWidth="1"/>
+    <col min="40" max="40" width="19.71" hidden="0" customWidth="1"/>
+    <col min="41" max="41" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -449,101 +663,1223 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
+        <v>46296</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46296</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
+        <v>41</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-44</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-26.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-51.4</v>
-      </c>
-      <c r="I2" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
+        <v>42</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21.1214724388276</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-21.1214724388276</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.1214724388276</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-21.1214724388276</v>
+      </c>
+      <c r="N2" t="n">
+        <v>21.1214724388276</v>
+      </c>
+      <c r="O2" t="n">
+        <v>7.71408057588472</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-7.71408057588472</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>25.8217332531286</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-25.8217332531286</v>
+      </c>
+      <c r="S2" t="n">
+        <v>84.7650968114332</v>
+      </c>
+      <c r="T2" t="n">
+        <v>52.9432846251304</v>
+      </c>
+      <c r="U2" t="n">
+        <v>31.8218121863028</v>
+      </c>
+      <c r="V2" t="n">
+        <v>14.9571416467823</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-14.9571416467823</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7.71408057588472</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>18.1076526772439</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.87327657259138</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>17.2481958662363</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
+        <v>46296</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46297</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
+        <v>49</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>31</v>
-      </c>
-      <c r="G3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="I3" t="n">
-        <v>79.9</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
+        <v>50</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-31.1958586890686</v>
+      </c>
+      <c r="K3" t="n">
+        <v>31.1958586890686</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-31.1958586890686</v>
+      </c>
+      <c r="M3" t="n">
+        <v>31.1958586890686</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-31.1958586890686</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-8.51342395243199</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8.51342395243199</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-38.2331456389508</v>
+      </c>
+      <c r="R3" t="n">
+        <v>38.2331456389508</v>
+      </c>
+      <c r="S3" t="n">
+        <v>83.8829678587598</v>
+      </c>
+      <c r="T3" t="n">
+        <v>26.3435545848456</v>
+      </c>
+      <c r="U3" t="n">
+        <v>57.5394132739142</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-20.4013126270395</v>
+      </c>
+      <c r="W3" t="n">
+        <v>20.4013126270395</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-8.51342395243199</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-29.7197216865188</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.307423688560876</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-31.5032823776294</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-11.3087336665131</v>
+      </c>
+      <c r="K4" t="n">
+        <v>11.3087336665131</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-11.3087336665131</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11.3087336665131</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-11.3087336665131</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-1.53420188500217</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.53420188500217</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-17.2814319498887</v>
+      </c>
+      <c r="R4" t="n">
+        <v>17.2814319498887</v>
+      </c>
+      <c r="S4" t="n">
+        <v>82.4571707186019</v>
+      </c>
+      <c r="T4" t="n">
+        <v>35.5742185260444</v>
+      </c>
+      <c r="U4" t="n">
+        <v>46.8829521925575</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-7.83309391095677</v>
+      </c>
+      <c r="W4" t="n">
+        <v>7.83309391095677</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-1.53420188500217</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-15.7472300648865</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.813577087875069</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-10.4951565786381</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29.5195665710122</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-29.5195665710122</v>
+      </c>
+      <c r="L5" t="n">
+        <v>29.5195665710122</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-29.5195665710122</v>
+      </c>
+      <c r="N5" t="n">
+        <v>29.5195665710122</v>
+      </c>
+      <c r="O5" t="n">
+        <v>10.1518322936632</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-10.1518322936632</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>29.7340341085703</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-29.7340341085703</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75.4967602907931</v>
+      </c>
+      <c r="T5" t="n">
+        <v>52.5081634309027</v>
+      </c>
+      <c r="U5" t="n">
+        <v>22.9885968598905</v>
+      </c>
+      <c r="V5" t="n">
+        <v>17.984713019626</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-17.984713019626</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10.1518322936632</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>19.5822018149071</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>5.59187458916986</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>23.9276919818424</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" t="n">
+        <v>13.939775151886</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-13.939775151886</v>
+      </c>
+      <c r="L6" t="n">
+        <v>13.939775151886</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-13.939775151886</v>
+      </c>
+      <c r="N6" t="n">
+        <v>13.939775151886</v>
+      </c>
+      <c r="O6" t="n">
+        <v>26.5983929993419</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-26.5983929993419</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>16.3523943043806</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-16.3523943043806</v>
+      </c>
+      <c r="S6" t="n">
+        <v>87.3813474834221</v>
+      </c>
+      <c r="T6" t="n">
+        <v>50.6605613176541</v>
+      </c>
+      <c r="U6" t="n">
+        <v>36.7207861657681</v>
+      </c>
+      <c r="V6" t="n">
+        <v>22.4999935213574</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-22.4999935213574</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>26.5983929993419</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-10.2459986949613</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3.99182830561121</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>9.94794684627481</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-16.081893520144</v>
+      </c>
+      <c r="K7" t="n">
+        <v>16.081893520144</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-16.081893520144</v>
+      </c>
+      <c r="M7" t="n">
+        <v>16.081893520144</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-16.081893520144</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.880803554516451</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.880803554516451</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-19.1015712057135</v>
+      </c>
+      <c r="R7" t="n">
+        <v>19.1015712057135</v>
+      </c>
+      <c r="S7" t="n">
+        <v>92.3403697870204</v>
+      </c>
+      <c r="T7" t="n">
+        <v>38.1292381334382</v>
+      </c>
+      <c r="U7" t="n">
+        <v>54.2111316535822</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-8.16911061499527</v>
+      </c>
+      <c r="W7" t="n">
+        <v>8.16911061499527</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.880803554516451</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-18.220767651197</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>8.62027637592669</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-24.7021698960707</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B8" s="1" t="n">
         <v>46299</v>
       </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I4" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
+      <c r="C8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" t="n">
+        <v>44.035980466128</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-44.035980466128</v>
+      </c>
+      <c r="L8" t="n">
+        <v>44.035980466128</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-44.035980466128</v>
+      </c>
+      <c r="N8" t="n">
+        <v>44.035980466128</v>
+      </c>
+      <c r="O8" t="n">
+        <v>26.5410631790021</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-26.5410631790021</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>51.4398780837789</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-51.4398780837789</v>
+      </c>
+      <c r="S8" t="n">
+        <v>85.5149845151073</v>
+      </c>
+      <c r="T8" t="n">
+        <v>64.7754824906176</v>
+      </c>
+      <c r="U8" t="n">
+        <v>20.7395020244896</v>
+      </c>
+      <c r="V8" t="n">
+        <v>36.5005891409128</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-36.5005891409128</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>26.5410631790021</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>24.8988149047767</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>17.66415126118</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>26.371829204948</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-31.0401014266216</v>
+      </c>
+      <c r="K9" t="n">
+        <v>31.0401014266216</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-31.0401014266216</v>
+      </c>
+      <c r="M9" t="n">
+        <v>31.0401014266216</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-31.0401014266216</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-19.7335017691576</v>
+      </c>
+      <c r="P9" t="n">
+        <v>19.7335017691576</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-31.6351276259966</v>
+      </c>
+      <c r="R9" t="n">
+        <v>31.6351276259966</v>
+      </c>
+      <c r="S9" t="n">
+        <v>79.8634775437564</v>
+      </c>
+      <c r="T9" t="n">
+        <v>24.4116880585674</v>
+      </c>
+      <c r="U9" t="n">
+        <v>55.451789485189</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-24.4941521118932</v>
+      </c>
+      <c r="W9" t="n">
+        <v>24.4941521118932</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-19.7335017691576</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-11.901625856839</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-22.1584577443541</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-8.88164368226755</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-11.287439349589</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.287439349589</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-11.287439349589</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11.287439349589</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-11.287439349589</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.796133574586188</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.796133574586188</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-9.04095819657352</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9.04095819657352</v>
+      </c>
+      <c r="S10" t="n">
+        <v>74.1632475937509</v>
+      </c>
+      <c r="T10" t="n">
+        <v>31.4379041220809</v>
+      </c>
+      <c r="U10" t="n">
+        <v>42.7253434716699</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-4.09406342338112</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4.09406342338112</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.796133574586188</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-8.24482462198733</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>5.26191961335821</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-16.5493589629472</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.975</v>
       </c>
     </row>
   </sheetData>
